--- a/src/src/main/webapp/portal/zkb/contractQuotaLog/APM_ZKB_Contract_quota_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/contractQuotaLog/APM_ZKB_Contract_quota_Template.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23127"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F525BF72-45CB-42D7-9FCD-0D4902E5EC1D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{652A7B97-9259-4AB4-8C59-24AB2053F5E3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>合同号</t>
   </si>
@@ -47,6 +47,9 @@
   </si>
   <si>
     <t>操作时间</t>
+  </si>
+  <si>
+    <t>名额类型</t>
   </si>
 </sst>
 </file>
@@ -380,21 +383,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.7109375" customWidth="1"/>
-    <col min="2" max="2" width="20.42578125" customWidth="1"/>
-    <col min="3" max="3" width="17" customWidth="1"/>
-    <col min="4" max="4" width="20" customWidth="1"/>
-    <col min="5" max="5" width="18.28515625" customWidth="1"/>
-    <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="26.140625" customWidth="1"/>
-    <col min="8" max="8" width="30.42578125" customWidth="1"/>
-    <col min="9" max="9" width="28.85546875" customWidth="1"/>
+    <col min="2" max="3" width="20.42578125" customWidth="1"/>
+    <col min="4" max="4" width="17" customWidth="1"/>
+    <col min="5" max="5" width="20" customWidth="1"/>
+    <col min="6" max="6" width="18.28515625" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" customWidth="1"/>
+    <col min="8" max="8" width="26.140625" customWidth="1"/>
+    <col min="9" max="9" width="30.42578125" customWidth="1"/>
+    <col min="10" max="10" width="28.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -402,24 +405,27 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
     </row>

--- a/src/src/main/webapp/portal/zkb/contractQuotaLog/APM_ZKB_Contract_quota_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/contractQuotaLog/APM_ZKB_Contract_quota_Template.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23127"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{652A7B97-9259-4AB4-8C59-24AB2053F5E3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E34EEC4B-935E-420C-87A4-D9D1350B69FD}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>合同号</t>
   </si>
@@ -50,6 +50,9 @@
   </si>
   <si>
     <t>名额类型</t>
+  </si>
+  <si>
+    <t>步骤</t>
   </si>
 </sst>
 </file>
@@ -383,21 +386,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:K1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.7109375" customWidth="1"/>
     <col min="2" max="3" width="20.42578125" customWidth="1"/>
-    <col min="4" max="4" width="17" customWidth="1"/>
-    <col min="5" max="5" width="20" customWidth="1"/>
-    <col min="6" max="6" width="18.28515625" customWidth="1"/>
-    <col min="7" max="7" width="18.7109375" customWidth="1"/>
-    <col min="8" max="8" width="26.140625" customWidth="1"/>
-    <col min="9" max="9" width="30.42578125" customWidth="1"/>
-    <col min="10" max="10" width="28.85546875" customWidth="1"/>
+    <col min="4" max="5" width="17" customWidth="1"/>
+    <col min="6" max="6" width="20" customWidth="1"/>
+    <col min="7" max="7" width="18.28515625" customWidth="1"/>
+    <col min="8" max="8" width="18.7109375" customWidth="1"/>
+    <col min="9" max="9" width="26.140625" customWidth="1"/>
+    <col min="10" max="10" width="30.42578125" customWidth="1"/>
+    <col min="11" max="11" width="28.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -411,21 +414,24 @@
         <v>2</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>8</v>
       </c>
     </row>
